--- a/Fase 1/Evidencias Grupales/PLANILLA DE EVALUACIÓN FASE 1.xlsx
+++ b/Fase 1/Evidencias Grupales/PLANILLA DE EVALUACIÓN FASE 1.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OwO\Documents\GitHub\CapStone\Fase 1\Evidencias Grupales\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Escritorio 2026\DUOC 2026-2\CAPSTONE\DOCUMENTOS POR FASE\DOCUMENTOS FASE1\EQUIPO 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E563A96-D9CB-4FA7-8E09-4EF24A04DE9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20520" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315"/>
   </bookViews>
   <sheets>
     <sheet name="EVALUACION1" sheetId="1" r:id="rId1"/>
@@ -45,7 +44,7 @@
     <definedName name="RE_TL">'RELEVANCIA-PUNTAJE'!$B$4</definedName>
     <definedName name="TL">'RELEVANCIA-PUNTAJE'!$B$2</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -389,7 +388,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -1149,7 +1148,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -1444,9 +1443,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:K929"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="66.85546875" customWidth="1"/>
@@ -3722,7 +3721,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Error de Ingreso - Nota debe estar entre 1,0 y 7,0" sqref="C4:E6" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Error de Ingreso - Nota debe estar entre 1,0 y 7,0" sqref="C4:E6">
       <formula1>1</formula1>
       <formula2>7</formula2>
     </dataValidation>
@@ -3732,7 +3731,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'RELEVANCIA-PUNTAJE'!$B$2:$E$2</xm:f>
           </x14:formula1>
@@ -3745,9 +3744,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC27BBF0-2056-4C6C-A496-F3E7DD799403}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.42578125" customWidth="1"/>
     <col min="2" max="2" width="40.28515625" customWidth="1"/>
@@ -3979,7 +3978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A14" s="42" t="s">
         <v>69</v>
       </c>
@@ -4039,7 +4038,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="102.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="90" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="38" t="s">
         <v>84</v>
       </c>
@@ -4085,9 +4084,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="21" width="10.7109375" customWidth="1"/>
   </cols>
@@ -6093,9 +6092,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
   </cols>
@@ -7485,9 +7484,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="22" width="10.7109375" customWidth="1"/>
   </cols>
@@ -8933,9 +8932,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="25" width="10.7109375" customWidth="1"/>
   </cols>
